--- a/GATEWAY/A1#111#MEDIANETSERVIZISRLX1/MedianetServizi/4Handy.it/2025.12/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#MEDIANETSERVIZISRLX1/MedianetServizi/4Handy.it/2025.12/accreditamento-checklist_V8.2.7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\A1#111#MEDIANETSERVIZISRLX1\MedianetServizi\4Handy.it\2025.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD1E206-5430-41FC-AE87-046660F95B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64033F6-4467-4B62-BE31-13B689ADD2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$51</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -81,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="327">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -1202,6 +1201,74 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.70.4.4.edd2859e5fb7a43c510695a407665149c8f34266c37e252ef70258600df83ac9.fe7b15dfcc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>Eccezione  durante la validazione del documento clinico FSE: timeout
+- Si sono verificati uno o più errori.
+Si è verificato un errore durante l'invio della richiesta.
+Continuare comunque con la generazione del Referto di Specialistica Ambulatoriale?</t>
+  </si>
+  <si>
+    <t>Nel caso di errore per i token JWT l'invio viene bloccato, ancora prima della generazione del documento, sarà il medico a contattare l'amministrazione per verificare eventuali errori di inserimento dei dati per la generazione del JWT</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell'anagrafica assistito, dove verrà evidenziato l'errore sul codice fiscale in minuscolo o con caratteri non conformi in modo tale da poter modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell'anagrafica assistito, modificare i campi evidenziati con errore, in questo caso il mancato inserimento del comune di residenza del paziente nella sezione indirizzo e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell'anagrafica assistito, modificare i campi evidenziando il mancato inserimento del nominativo, e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell'anagrafica assistito, modificare i campi evidenziati con errore, in questo caso la compilazione del sesso e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento legata all' assistito in questo caso verrà indicata la sezione di prescrizione farmacologica, modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio,altrimenti verrà gestito dalla nostra assistenza insieme al medico compilatore.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito verrà evidenziata la sezione prestazioni dove verrà indicato la mancata compilazione dell'informazione inerente alla tipologia di esame in questione, modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento  assistito nella sezione referto, modificare il  campo e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito deove verrà indicato il quesito diagnostico, modificare il campo narrativo e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito riguardante le prestazione, modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio. Altrimenti verrà gestito dalla nostra assistenza in caso di ulteriore segnalazione di errore</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito nella sezione storia clinica, modificare i campi legati all'anamnesi patologica e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito evidenziando la sezione che ha dato errore Storia Clinica, modificare i campi di parentela del familaire in oggetto e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito, verrà segnalata la sezione Storia Clinica con il campo legato all'intervallo di tempo di allergia o intolleranza presente, modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito dove verrà evidenziata l'assenza della specifica inerente all'agente che ha scatenato l'allergia, modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell' assistito, modificare i campi della diagnosi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio. Altrimenti verrà gestito dalla nostra assistenza verificando l'esistenza del codice corretto della diagnosi, in caso di non presenza del codice si procederà ad aggiungerlo..</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. L'elemento verrà valorizzato in backoffice dalla nostra assistenza dopo le verifiche del caso e presentata una coda di retry….</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell'assistito, modificare il campo inerente all'osservazione clinica legata ad un parente biologico e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio. Nel caso l'errore persista, verrà effettuato un controllo sul codice dalla nostra assistenza e in caso di mancata valorizzazione si provvederà all'aggiunta...</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato.Nel caso del mancato inserimento del livello di riservatezza del documento, l'invio verrà gestito in backoffice dopo aver verificato.</t>
+  </si>
+  <si>
+    <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento della richiesta nella ricetta dell' assistito, modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio. Nel caso il codice continui a generare errore si procederà a modificarlo con quello corretto e presentare una coda di retry dalla nostra assistenza...</t>
+  </si>
+  <si>
+    <t>L' applicativo mostra all' operatore/medico l' errore indicato , è data la possibilità comunque di continuare con la gestione del referto oppure annullare e ripetere l' operazione di generazione del referto e di conseguenza la validazione.
+Se l' operatore sceglie di continuare l' applicativo provvederà ad inserire in una coda automaitica per ripetere successivamente la validazione del documento .
+Se l' errore si risolve correggendo dati mancanti o non corretti il referto può essere rigenerato dall' operatore/medico di competenza  , per altri tipi di errori  si chiede nel caso supporto ai tecnici dell' applicativo.</t>
   </si>
 </sst>
 </file>
@@ -3599,10 +3666,18 @@
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
       <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
+      <c r="P11" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q11" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="R11" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="S11" s="35" t="s">
+        <v>307</v>
+      </c>
       <c r="T11" s="35"/>
       <c r="U11" s="36"/>
       <c r="V11" s="37"/>
@@ -3681,10 +3756,18 @@
       <c r="M13" s="35"/>
       <c r="N13" s="35"/>
       <c r="O13" s="35"/>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
+      <c r="P13" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q13" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="R13" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="S13" s="35" t="s">
+        <v>307</v>
+      </c>
       <c r="T13" s="35"/>
       <c r="U13" s="36"/>
       <c r="V13" s="37"/>
@@ -3779,7 +3862,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="35" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="P15" s="35" t="s">
         <v>95</v>
@@ -3791,7 +3874,7 @@
         <v>95</v>
       </c>
       <c r="S15" s="35" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="T15" s="35"/>
       <c r="U15" s="36" t="s">
@@ -3854,7 +3937,7 @@
         <v>51</v>
       </c>
       <c r="S16" s="35" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="T16" s="35" t="s">
         <v>93</v>
@@ -3917,7 +4000,7 @@
         <v>51</v>
       </c>
       <c r="S17" s="35" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="T17" s="35" t="s">
         <v>93</v>
@@ -3980,7 +4063,7 @@
         <v>51</v>
       </c>
       <c r="S18" s="35" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="T18" s="35" t="s">
         <v>93</v>
@@ -4043,7 +4126,7 @@
         <v>51</v>
       </c>
       <c r="S19" s="35" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="T19" s="35" t="s">
         <v>93</v>
@@ -4097,7 +4180,7 @@
         <v>293</v>
       </c>
       <c r="P20" s="35" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="Q20" s="35" t="s">
         <v>95</v>
@@ -4106,7 +4189,7 @@
         <v>51</v>
       </c>
       <c r="S20" s="35" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="T20" s="35" t="s">
         <v>93</v>
@@ -4169,7 +4252,7 @@
         <v>51</v>
       </c>
       <c r="S21" s="35" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="T21" s="35" t="s">
         <v>93</v>
@@ -4232,7 +4315,7 @@
         <v>51</v>
       </c>
       <c r="S22" s="35" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="T22" s="35" t="s">
         <v>93</v>
@@ -4295,7 +4378,7 @@
         <v>51</v>
       </c>
       <c r="S23" s="35" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="T23" s="35" t="s">
         <v>93</v>
@@ -4349,7 +4432,7 @@
         <v>293</v>
       </c>
       <c r="P24" s="35" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="Q24" s="35" t="s">
         <v>95</v>
@@ -4358,7 +4441,7 @@
         <v>51</v>
       </c>
       <c r="S24" s="35" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="T24" s="35" t="s">
         <v>93</v>
@@ -4421,7 +4504,7 @@
         <v>51</v>
       </c>
       <c r="S25" s="35" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="T25" s="35" t="s">
         <v>93</v>
@@ -4484,7 +4567,7 @@
         <v>51</v>
       </c>
       <c r="S26" s="35" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="T26" s="35" t="s">
         <v>93</v>
@@ -4547,7 +4630,7 @@
         <v>51</v>
       </c>
       <c r="S27" s="35" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="T27" s="35" t="s">
         <v>93</v>
@@ -4610,7 +4693,7 @@
         <v>51</v>
       </c>
       <c r="S28" s="35" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="T28" s="35" t="s">
         <v>93</v>
@@ -4664,7 +4747,7 @@
         <v>293</v>
       </c>
       <c r="P29" s="35" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="Q29" s="35" t="s">
         <v>95</v>
@@ -4673,7 +4756,7 @@
         <v>51</v>
       </c>
       <c r="S29" s="35" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="T29" s="35" t="s">
         <v>93</v>
@@ -4727,16 +4810,16 @@
         <v>293</v>
       </c>
       <c r="P30" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q30" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="R30" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="Q30" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="R30" s="35" t="s">
-        <v>51</v>
-      </c>
       <c r="S30" s="35" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="T30" s="35" t="s">
         <v>93</v>
@@ -5832,7 +5915,7 @@
         <v>293</v>
       </c>
       <c r="P48" s="35" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="Q48" s="35" t="s">
         <v>95</v>
@@ -5841,7 +5924,7 @@
         <v>51</v>
       </c>
       <c r="S48" s="33" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="T48" s="35" t="s">
         <v>93</v>
@@ -5895,7 +5978,7 @@
         <v>293</v>
       </c>
       <c r="P49" s="35" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="Q49" s="35" t="s">
         <v>95</v>
@@ -5904,7 +5987,7 @@
         <v>51</v>
       </c>
       <c r="S49" s="33" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="T49" s="35" t="s">
         <v>93</v>
@@ -6021,16 +6104,16 @@
         <v>293</v>
       </c>
       <c r="P51" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q51" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="R51" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="Q51" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="R51" s="35" t="s">
-        <v>51</v>
-      </c>
       <c r="S51" s="35" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="T51" s="35" t="s">
         <v>93</v>
@@ -12415,21 +12498,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -12573,32 +12641,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12616,6 +12674,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/A1#111#MEDIANETSERVIZISRLX1/MedianetServizi/4Handy.it/2025.12/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#MEDIANETSERVIZISRLX1/MedianetServizi/4Handy.it/2025.12/accreditamento-checklist_V8.2.7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\A1#111#MEDIANETSERVIZISRLX1\MedianetServizi\4Handy.it\2025.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A64033F6-4467-4B62-BE31-13B689ADD2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FAA8D2-90F3-4A3A-A62C-9B881E99B7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="326">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -1207,9 +1207,6 @@
 - Si sono verificati uno o più errori.
 Si è verificato un errore durante l'invio della richiesta.
 Continuare comunque con la generazione del Referto di Specialistica Ambulatoriale?</t>
-  </si>
-  <si>
-    <t>Nel caso di errore per i token JWT l'invio viene bloccato, ancora prima della generazione del documento, sarà il medico a contattare l'amministrazione per verificare eventuali errori di inserimento dei dati per la generazione del JWT</t>
   </si>
   <si>
     <t>L'invio del documento  viene bloccato. Sarà il medico ad aprire la pagina di riferimento dell'anagrafica assistito, dove verrà evidenziato l'errore sul codice fiscale in minuscolo o con caratteri non conformi in modo tale da poter modificare i campi e ritentare manualmente l'invio del documento dal nostro applicativo, se non verrannò riscontrati ulteriori errori si procede con l'invio.</t>
@@ -3675,9 +3672,7 @@
       <c r="R11" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="S11" s="35" t="s">
-        <v>307</v>
-      </c>
+      <c r="S11" s="35"/>
       <c r="T11" s="35"/>
       <c r="U11" s="36"/>
       <c r="V11" s="37"/>
@@ -3765,9 +3760,7 @@
       <c r="R13" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="S13" s="35" t="s">
-        <v>307</v>
-      </c>
+      <c r="S13" s="35"/>
       <c r="T13" s="35"/>
       <c r="U13" s="36"/>
       <c r="V13" s="37"/>
@@ -3874,7 +3867,7 @@
         <v>95</v>
       </c>
       <c r="S15" s="35" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="T15" s="35"/>
       <c r="U15" s="36" t="s">
@@ -3937,7 +3930,7 @@
         <v>51</v>
       </c>
       <c r="S16" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="T16" s="35" t="s">
         <v>93</v>
@@ -4000,7 +3993,7 @@
         <v>51</v>
       </c>
       <c r="S17" s="35" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="T17" s="35" t="s">
         <v>93</v>
@@ -4063,7 +4056,7 @@
         <v>51</v>
       </c>
       <c r="S18" s="35" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="T18" s="35" t="s">
         <v>93</v>
@@ -4126,7 +4119,7 @@
         <v>51</v>
       </c>
       <c r="S19" s="35" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="T19" s="35" t="s">
         <v>93</v>
@@ -4189,7 +4182,7 @@
         <v>51</v>
       </c>
       <c r="S20" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="T20" s="35" t="s">
         <v>93</v>
@@ -4252,7 +4245,7 @@
         <v>51</v>
       </c>
       <c r="S21" s="35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="T21" s="35" t="s">
         <v>93</v>
@@ -4315,7 +4308,7 @@
         <v>51</v>
       </c>
       <c r="S22" s="35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="T22" s="35" t="s">
         <v>93</v>
@@ -4378,7 +4371,7 @@
         <v>51</v>
       </c>
       <c r="S23" s="35" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T23" s="35" t="s">
         <v>93</v>
@@ -4441,7 +4434,7 @@
         <v>51</v>
       </c>
       <c r="S24" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="T24" s="35" t="s">
         <v>93</v>
@@ -4504,7 +4497,7 @@
         <v>51</v>
       </c>
       <c r="S25" s="35" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="T25" s="35" t="s">
         <v>93</v>
@@ -4567,7 +4560,7 @@
         <v>51</v>
       </c>
       <c r="S26" s="35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="T26" s="35" t="s">
         <v>93</v>
@@ -4630,7 +4623,7 @@
         <v>51</v>
       </c>
       <c r="S27" s="35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T27" s="35" t="s">
         <v>93</v>
@@ -4693,7 +4686,7 @@
         <v>51</v>
       </c>
       <c r="S28" s="35" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="T28" s="35" t="s">
         <v>93</v>
@@ -4756,7 +4749,7 @@
         <v>51</v>
       </c>
       <c r="S29" s="35" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="T29" s="35" t="s">
         <v>93</v>
@@ -4819,7 +4812,7 @@
         <v>95</v>
       </c>
       <c r="S30" s="35" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T30" s="35" t="s">
         <v>93</v>
@@ -5924,7 +5917,7 @@
         <v>51</v>
       </c>
       <c r="S48" s="33" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="T48" s="35" t="s">
         <v>93</v>
@@ -5987,7 +5980,7 @@
         <v>51</v>
       </c>
       <c r="S49" s="33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T49" s="35" t="s">
         <v>93</v>
@@ -6113,7 +6106,7 @@
         <v>95</v>
       </c>
       <c r="S51" s="35" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="T51" s="35" t="s">
         <v>93</v>
@@ -12498,6 +12491,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -12641,22 +12649,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12674,31 +12692,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>

--- a/GATEWAY/A1#111#MEDIANETSERVIZISRLX1/MedianetServizi/4Handy.it/2025.12/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111#MEDIANETSERVIZISRLX1/MedianetServizi/4Handy.it/2025.12/accreditamento-checklist_V8.2.7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\A1#111#MEDIANETSERVIZISRLX1\MedianetServizi\4Handy.it\2025.12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FAA8D2-90F3-4A3A-A62C-9B881E99B7F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB54EF0-F72D-4D0B-B540-A3D61EA29FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="326">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -3663,15 +3663,9 @@
       <c r="M11" s="35"/>
       <c r="N11" s="35"/>
       <c r="O11" s="35"/>
-      <c r="P11" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q11" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>95</v>
-      </c>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
       <c r="S11" s="35"/>
       <c r="T11" s="35"/>
       <c r="U11" s="36"/>
@@ -3751,15 +3745,9 @@
       <c r="M13" s="35"/>
       <c r="N13" s="35"/>
       <c r="O13" s="35"/>
-      <c r="P13" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>95</v>
-      </c>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
       <c r="S13" s="35"/>
       <c r="T13" s="35"/>
       <c r="U13" s="36"/>
@@ -12491,21 +12479,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -12649,32 +12622,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12692,6 +12655,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
